--- a/public/outsoucrd apple sheet.xlsx
+++ b/public/outsoucrd apple sheet.xlsx
@@ -493,8 +493,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H51"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:H55"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -551,7 +551,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>iPhone 3G</t>
+          <t>iPhone</t>
         </is>
       </c>
       <c r="B2" s="4" t="n">
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="E2" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),325.7)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),339.75)</f>
         <v/>
       </c>
       <c r="F2" s="6">
@@ -598,7 +598,7 @@
         <v/>
       </c>
       <c r="E3" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),325.7)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),339.75)</f>
         <v/>
       </c>
       <c r="F3" s="6">
@@ -631,7 +631,7 @@
         <v/>
       </c>
       <c r="E4" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),325.7)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),339.75)</f>
         <v/>
       </c>
       <c r="F4" s="6">
@@ -664,7 +664,7 @@
         <v/>
       </c>
       <c r="E5" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),325.7)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),339.75)</f>
         <v/>
       </c>
       <c r="F5" s="6">
@@ -697,7 +697,7 @@
         <v/>
       </c>
       <c r="E6" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),325.7)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),339.75)</f>
         <v/>
       </c>
       <c r="F6" s="6">
@@ -730,7 +730,7 @@
         <v/>
       </c>
       <c r="E7" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),325.7)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),339.75)</f>
         <v/>
       </c>
       <c r="F7" s="6">
@@ -753,17 +753,17 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>41538</v>
+        <v>41537</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>649</v>
       </c>
       <c r="D8" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B8), 2, 2)"),17.52)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B8), 2, 2)"),16.69)</f>
         <v/>
       </c>
       <c r="E8" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),325.7)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),339.75)</f>
         <v/>
       </c>
       <c r="F8" s="6">
@@ -796,7 +796,7 @@
         <v/>
       </c>
       <c r="E9" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),325.7)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),339.75)</f>
         <v/>
       </c>
       <c r="F9" s="6">
@@ -829,7 +829,7 @@
         <v/>
       </c>
       <c r="E10" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),325.7)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),339.75)</f>
         <v/>
       </c>
       <c r="F10" s="6">
@@ -848,7 +848,7 @@
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>iPhone 6S</t>
+          <t>iPhone 6s</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
@@ -862,7 +862,7 @@
         <v/>
       </c>
       <c r="E11" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),325.7)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),339.75)</f>
         <v/>
       </c>
       <c r="F11" s="6">
@@ -881,7 +881,7 @@
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>iPhone 6S Plus</t>
+          <t>iPhone 6s Plus</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
@@ -895,7 +895,7 @@
         <v/>
       </c>
       <c r="E12" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),325.7)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),339.75)</f>
         <v/>
       </c>
       <c r="F12" s="6">
@@ -914,21 +914,21 @@
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>iPhone 7</t>
+          <t>iPhone SE</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>42629</v>
+        <v>42460</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>649</v>
+        <v>399</v>
       </c>
       <c r="D13" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B13), 2, 2)"),28.73)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B13), 2, 2)"),27.25)</f>
         <v/>
       </c>
       <c r="E13" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),325.7)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),339.75)</f>
         <v/>
       </c>
       <c r="F13" s="6">
@@ -947,21 +947,21 @@
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>iPhone 7 Plus</t>
+          <t>iPhone 7</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
         <v>42629</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>769</v>
+        <v>649</v>
       </c>
       <c r="D14" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B14), 2, 2)"),28.73)</f>
         <v/>
       </c>
       <c r="E14" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),325.7)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),339.75)</f>
         <v/>
       </c>
       <c r="F14" s="6">
@@ -980,21 +980,21 @@
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>iPhone 8</t>
+          <t>iPhone 7 Plus</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>43000</v>
+        <v>42629</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>699</v>
+        <v>769</v>
       </c>
       <c r="D15" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B15), 2, 2)"),37.97)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B15), 2, 2)"),28.73)</f>
         <v/>
       </c>
       <c r="E15" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),325.7)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),339.75)</f>
         <v/>
       </c>
       <c r="F15" s="6">
@@ -1013,21 +1013,21 @@
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>iPhone 8 Plus</t>
+          <t>iPhone 8</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
         <v>43000</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>799</v>
+        <v>699</v>
       </c>
       <c r="D16" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B16), 2, 2)"),37.97)</f>
         <v/>
       </c>
       <c r="E16" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),325.7)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),339.75)</f>
         <v/>
       </c>
       <c r="F16" s="6">
@@ -1046,21 +1046,21 @@
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>iPhone X</t>
+          <t>iPhone 8 Plus</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>43042</v>
+        <v>43000</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>999</v>
+        <v>799</v>
       </c>
       <c r="D17" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B17), 2, 2)"),43.13)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B17), 2, 2)"),37.97)</f>
         <v/>
       </c>
       <c r="E17" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),325.7)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),339.75)</f>
         <v/>
       </c>
       <c r="F17" s="6">
@@ -1079,21 +1079,21 @@
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>iPhone XS</t>
+          <t>iPhone X</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>43364</v>
+        <v>43042</v>
       </c>
       <c r="C18" s="5" t="n">
         <v>999</v>
       </c>
       <c r="D18" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B18), 2, 2)"),54.42)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B18), 2, 2)"),43.13)</f>
         <v/>
       </c>
       <c r="E18" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),325.7)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),339.75)</f>
         <v/>
       </c>
       <c r="F18" s="6">
@@ -1112,21 +1112,21 @@
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>iPhone XS Max</t>
+          <t>iPhone XS</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>43364</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1099</v>
+        <v>999</v>
       </c>
       <c r="D19" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B19), 2, 2)"),54.42)</f>
         <v/>
       </c>
       <c r="E19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),325.7)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),339.75)</f>
         <v/>
       </c>
       <c r="F19" s="6">
@@ -1145,21 +1145,21 @@
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>iPhone XR</t>
+          <t>iPhone XS Max</t>
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>43399</v>
+        <v>43364</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>749</v>
+        <v>1099</v>
       </c>
       <c r="D20" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B20), 2, 2)"),54.08)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B20), 2, 2)"),54.42)</f>
         <v/>
       </c>
       <c r="E20" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),325.7)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),339.75)</f>
         <v/>
       </c>
       <c r="F20" s="6">
@@ -1178,21 +1178,21 @@
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>iPhone 11</t>
+          <t>iPhone XR</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>43728</v>
+        <v>43399</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>699</v>
+        <v>749</v>
       </c>
       <c r="D21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B21), 2, 2)"),54.43)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B21), 2, 2)"),54.08)</f>
         <v/>
       </c>
       <c r="E21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),325.7)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),339.75)</f>
         <v/>
       </c>
       <c r="F21" s="6">
@@ -1211,21 +1211,21 @@
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>iPhone 11 Pro</t>
+          <t>iPhone 11</t>
         </is>
       </c>
       <c r="B22" s="4" t="n">
         <v>43728</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>999</v>
+        <v>699</v>
       </c>
       <c r="D22" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B22), 2, 2)"),54.43)</f>
         <v/>
       </c>
       <c r="E22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),325.7)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),339.75)</f>
         <v/>
       </c>
       <c r="F22" s="6">
@@ -1244,21 +1244,21 @@
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>iPhone 11 Pro Max</t>
+          <t>iPhone 11 Pro</t>
         </is>
       </c>
       <c r="B23" s="4" t="n">
         <v>43728</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>1099</v>
+        <v>999</v>
       </c>
       <c r="D23" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B23), 2, 2)"),54.43)</f>
         <v/>
       </c>
       <c r="E23" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),325.7)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),339.75)</f>
         <v/>
       </c>
       <c r="F23" s="6">
@@ -1277,21 +1277,21 @@
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>iPhone SE 2</t>
+          <t>iPhone 11 Pro Max</t>
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>43945</v>
+        <v>43728</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>399</v>
+        <v>1099</v>
       </c>
       <c r="D24" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B24), 2, 2)"),70.74)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B24), 2, 2)"),54.43)</f>
         <v/>
       </c>
       <c r="E24" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),325.7)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),339.75)</f>
         <v/>
       </c>
       <c r="F24" s="6">
@@ -1310,21 +1310,21 @@
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>iPhone 12</t>
+          <t>iPhone SE (2nd gen)</t>
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>44148</v>
+        <v>43945</v>
       </c>
       <c r="C25" s="5" t="n">
-        <v>799</v>
+        <v>399</v>
       </c>
       <c r="D25" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B25), 2, 2)"),119.26)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B25), 2, 2)"),70.74)</f>
         <v/>
       </c>
       <c r="E25" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),325.7)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),339.75)</f>
         <v/>
       </c>
       <c r="F25" s="6">
@@ -1343,21 +1343,21 @@
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>iPhone 12 Mini</t>
+          <t>iPhone 12</t>
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>44148</v>
+        <v>44127</v>
       </c>
       <c r="C26" s="5" t="n">
-        <v>699</v>
+        <v>799</v>
       </c>
       <c r="D26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B26), 2, 2)"),119.26)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B26), 2, 2)"),115.04)</f>
         <v/>
       </c>
       <c r="E26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),325.7)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),339.75)</f>
         <v/>
       </c>
       <c r="F26" s="6">
@@ -1380,17 +1380,17 @@
         </is>
       </c>
       <c r="B27" s="4" t="n">
-        <v>44148</v>
+        <v>44127</v>
       </c>
       <c r="C27" s="5" t="n">
         <v>999</v>
       </c>
       <c r="D27" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B27), 2, 2)"),119.26)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B27), 2, 2)"),115.04)</f>
         <v/>
       </c>
       <c r="E27" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),325.7)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),339.75)</f>
         <v/>
       </c>
       <c r="F27" s="6">
@@ -1409,21 +1409,21 @@
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>iPhone 12 Pro Max</t>
+          <t>iPhone 12 mini</t>
         </is>
       </c>
       <c r="B28" s="4" t="n">
         <v>44148</v>
       </c>
       <c r="C28" s="5" t="n">
-        <v>1099</v>
+        <v>699</v>
       </c>
       <c r="D28" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B28), 2, 2)"),119.26)</f>
         <v/>
       </c>
       <c r="E28" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),325.7)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),339.75)</f>
         <v/>
       </c>
       <c r="F28" s="6">
@@ -1442,21 +1442,21 @@
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>iPhone 13</t>
+          <t>iPhone 12 Pro Max</t>
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>44463</v>
+        <v>44148</v>
       </c>
       <c r="C29" s="5" t="n">
-        <v>799</v>
+        <v>1099</v>
       </c>
       <c r="D29" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B29), 2, 2)"),146.92)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B29), 2, 2)"),119.26)</f>
         <v/>
       </c>
       <c r="E29" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),325.7)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),339.75)</f>
         <v/>
       </c>
       <c r="F29" s="6">
@@ -1475,21 +1475,21 @@
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>iPhone 13 Mini</t>
+          <t>iPhone 13</t>
         </is>
       </c>
       <c r="B30" s="4" t="n">
         <v>44463</v>
       </c>
       <c r="C30" s="5" t="n">
-        <v>699</v>
+        <v>799</v>
       </c>
       <c r="D30" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B30), 2, 2)"),146.92)</f>
         <v/>
       </c>
       <c r="E30" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),325.7)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),339.75)</f>
         <v/>
       </c>
       <c r="F30" s="6">
@@ -1508,21 +1508,21 @@
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>iPhone 13 Pro</t>
+          <t>iPhone 13 mini</t>
         </is>
       </c>
       <c r="B31" s="4" t="n">
         <v>44463</v>
       </c>
       <c r="C31" s="5" t="n">
-        <v>999</v>
+        <v>699</v>
       </c>
       <c r="D31" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B31), 2, 2)"),146.92)</f>
         <v/>
       </c>
       <c r="E31" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),325.7)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),339.75)</f>
         <v/>
       </c>
       <c r="F31" s="6">
@@ -1541,21 +1541,21 @@
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>iPhone 13 Pro Max</t>
+          <t>iPhone 13 Pro</t>
         </is>
       </c>
       <c r="B32" s="4" t="n">
         <v>44463</v>
       </c>
       <c r="C32" s="5" t="n">
-        <v>1099</v>
+        <v>999</v>
       </c>
       <c r="D32" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B32), 2, 2)"),146.92)</f>
         <v/>
       </c>
       <c r="E32" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),325.7)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),339.75)</f>
         <v/>
       </c>
       <c r="F32" s="6">
@@ -1574,21 +1574,21 @@
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>iPhone SE 3</t>
+          <t>iPhone 13 Pro Max</t>
         </is>
       </c>
       <c r="B33" s="4" t="n">
-        <v>44638</v>
+        <v>44463</v>
       </c>
       <c r="C33" s="5" t="n">
-        <v>429</v>
+        <v>1099</v>
       </c>
       <c r="D33" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B33), 2, 2)"),163.98)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B33), 2, 2)"),146.92)</f>
         <v/>
       </c>
       <c r="E33" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),325.7)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),339.75)</f>
         <v/>
       </c>
       <c r="F33" s="6">
@@ -1607,21 +1607,21 @@
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>iPhone 14</t>
+          <t>iPhone SE (3rd gen)</t>
         </is>
       </c>
       <c r="B34" s="4" t="n">
-        <v>44841</v>
+        <v>44638</v>
       </c>
       <c r="C34" s="5" t="n">
-        <v>799</v>
+        <v>429</v>
       </c>
       <c r="D34" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B34), 2, 2)"),140.09)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B34), 2, 2)"),163.98)</f>
         <v/>
       </c>
       <c r="E34" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),325.7)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),339.75)</f>
         <v/>
       </c>
       <c r="F34" s="6">
@@ -1640,21 +1640,21 @@
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>iPhone 14 Plus</t>
+          <t>iPhone 14</t>
         </is>
       </c>
       <c r="B35" s="4" t="n">
-        <v>44841</v>
+        <v>44820</v>
       </c>
       <c r="C35" s="5" t="n">
-        <v>899</v>
+        <v>799</v>
       </c>
       <c r="D35" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B35), 2, 2)"),140.09)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B35), 2, 2)"),150.7)</f>
         <v/>
       </c>
       <c r="E35" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),325.7)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),339.75)</f>
         <v/>
       </c>
       <c r="F35" s="6">
@@ -1677,17 +1677,17 @@
         </is>
       </c>
       <c r="B36" s="4" t="n">
-        <v>44841</v>
+        <v>44820</v>
       </c>
       <c r="C36" s="5" t="n">
         <v>999</v>
       </c>
       <c r="D36" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B36), 2, 2)"),140.09)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B36), 2, 2)"),150.7)</f>
         <v/>
       </c>
       <c r="E36" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),325.7)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),339.75)</f>
         <v/>
       </c>
       <c r="F36" s="6">
@@ -1710,17 +1710,17 @@
         </is>
       </c>
       <c r="B37" s="4" t="n">
-        <v>44841</v>
+        <v>44820</v>
       </c>
       <c r="C37" s="5" t="n">
         <v>1099</v>
       </c>
       <c r="D37" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B37), 2, 2)"),140.09)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B37), 2, 2)"),150.7)</f>
         <v/>
       </c>
       <c r="E37" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),325.7)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),339.75)</f>
         <v/>
       </c>
       <c r="F37" s="6">
@@ -1739,21 +1739,21 @@
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>iPhone 15</t>
+          <t>iPhone 14 Plus</t>
         </is>
       </c>
       <c r="B38" s="4" t="n">
-        <v>45191</v>
+        <v>44841</v>
       </c>
       <c r="C38" s="5" t="n">
-        <v>799</v>
+        <v>899</v>
       </c>
       <c r="D38" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B38), 2, 2)"),174.79)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B38), 2, 2)"),140.09)</f>
         <v/>
       </c>
       <c r="E38" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),325.7)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),339.75)</f>
         <v/>
       </c>
       <c r="F38" s="6">
@@ -1772,21 +1772,21 @@
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>iPhone 15 Plus</t>
+          <t>iPhone 15</t>
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>45192</v>
+        <v>45191</v>
       </c>
       <c r="C39" s="5" t="n">
-        <v>899</v>
+        <v>799</v>
       </c>
       <c r="D39" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B39), 2, 2)"),176.08)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B39), 2, 2)"),174.79)</f>
         <v/>
       </c>
       <c r="E39" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),325.7)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),339.75)</f>
         <v/>
       </c>
       <c r="F39" s="6">
@@ -1805,21 +1805,21 @@
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>iPhone 15 Pro</t>
+          <t>iPhone 15 Plus</t>
         </is>
       </c>
       <c r="B40" s="4" t="n">
-        <v>45193</v>
+        <v>45191</v>
       </c>
       <c r="C40" s="5" t="n">
-        <v>999</v>
+        <v>899</v>
       </c>
       <c r="D40" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B40), 2, 2)"),176.08)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B40), 2, 2)"),174.79)</f>
         <v/>
       </c>
       <c r="E40" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),325.7)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),339.75)</f>
         <v/>
       </c>
       <c r="F40" s="6">
@@ -1838,21 +1838,21 @@
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>iPhone 15 Pro Max</t>
+          <t>iPhone 15 Pro</t>
         </is>
       </c>
       <c r="B41" s="4" t="n">
-        <v>45194</v>
+        <v>45191</v>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1199</v>
+        <v>999</v>
       </c>
       <c r="D41" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B41), 2, 2)"),176.08)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B41), 2, 2)"),174.79)</f>
         <v/>
       </c>
       <c r="E41" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),325.7)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),339.75)</f>
         <v/>
       </c>
       <c r="F41" s="6">
@@ -1871,21 +1871,21 @@
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>iPhone 16</t>
+          <t>iPhone 15 Pro Max</t>
         </is>
       </c>
       <c r="B42" s="4" t="n">
-        <v>45555</v>
+        <v>45191</v>
       </c>
       <c r="C42" s="5" t="n">
-        <v>799</v>
+        <v>1199</v>
       </c>
       <c r="D42" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B42), 2, 2)"),226.31)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B42), 2, 2)"),174.79)</f>
         <v/>
       </c>
       <c r="E42" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),325.7)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),339.75)</f>
         <v/>
       </c>
       <c r="F42" s="6">
@@ -1904,21 +1904,21 @@
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>iPhone 16 Plus</t>
+          <t>iPhone 16</t>
         </is>
       </c>
       <c r="B43" s="4" t="n">
         <v>45555</v>
       </c>
       <c r="C43" s="5" t="n">
-        <v>899</v>
+        <v>799</v>
       </c>
       <c r="D43" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B43), 2, 2)"),226.31)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B43), 2, 2)"),228.2)</f>
         <v/>
       </c>
       <c r="E43" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),325.7)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),339.75)</f>
         <v/>
       </c>
       <c r="F43" s="6">
@@ -1937,21 +1937,21 @@
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>iPhone 16 Pro</t>
+          <t>iPhone 16 Plus</t>
         </is>
       </c>
       <c r="B44" s="4" t="n">
         <v>45555</v>
       </c>
       <c r="C44" s="5" t="n">
-        <v>999</v>
+        <v>899</v>
       </c>
       <c r="D44" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B44), 2, 2)"),226.31)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B44), 2, 2)"),228.2)</f>
         <v/>
       </c>
       <c r="E44" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),325.7)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),339.75)</f>
         <v/>
       </c>
       <c r="F44" s="6">
@@ -1970,21 +1970,21 @@
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>iPhone 16 Pro Max</t>
+          <t>iPhone 16 Pro</t>
         </is>
       </c>
       <c r="B45" s="4" t="n">
         <v>45555</v>
       </c>
       <c r="C45" s="5" t="n">
-        <v>1199</v>
+        <v>999</v>
       </c>
       <c r="D45" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B45), 2, 2)"),226.31)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B45), 2, 2)"),228.2)</f>
         <v/>
       </c>
       <c r="E45" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),325.7)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),339.75)</f>
         <v/>
       </c>
       <c r="F45" s="6">
@@ -2003,21 +2003,21 @@
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>iPhone 17</t>
+          <t>iPhone 16 Pro Max</t>
         </is>
       </c>
       <c r="B46" s="4" t="n">
-        <v>45919</v>
+        <v>45555</v>
       </c>
       <c r="C46" s="5" t="n">
-        <v>799</v>
+        <v>1199</v>
       </c>
       <c r="D46" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B46), 2, 2)"),244.6)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B46), 2, 2)"),228.2)</f>
         <v/>
       </c>
       <c r="E46" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),325.7)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),339.75)</f>
         <v/>
       </c>
       <c r="F46" s="6">
@@ -2036,21 +2036,21 @@
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>iPhone Air</t>
+          <t>iPhone 16e</t>
         </is>
       </c>
       <c r="B47" s="4" t="n">
-        <v>45919</v>
+        <v>45716</v>
       </c>
       <c r="C47" s="5" t="n">
-        <v>999</v>
+        <v>599</v>
       </c>
       <c r="D47" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B47), 2, 2)"),244.6)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B47), 2, 2)"),241.84)</f>
         <v/>
       </c>
       <c r="E47" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),325.7)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),339.75)</f>
         <v/>
       </c>
       <c r="F47" s="6">
@@ -2069,21 +2069,21 @@
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro</t>
+          <t>iPhone 17</t>
         </is>
       </c>
       <c r="B48" s="4" t="n">
         <v>45919</v>
       </c>
       <c r="C48" s="5" t="n">
-        <v>1099</v>
+        <v>799</v>
       </c>
       <c r="D48" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B48), 2, 2)"),244.6)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B48), 2, 2)"),245.5)</f>
         <v/>
       </c>
       <c r="E48" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),325.7)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),339.75)</f>
         <v/>
       </c>
       <c r="F48" s="6">
@@ -2102,21 +2102,21 @@
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro Max</t>
+          <t>iPhone Air</t>
         </is>
       </c>
       <c r="B49" s="4" t="n">
         <v>45919</v>
       </c>
       <c r="C49" s="5" t="n">
-        <v>1199</v>
+        <v>999</v>
       </c>
       <c r="D49" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B49), 2, 2)"),244.6)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B49), 2, 2)"),245.5)</f>
         <v/>
       </c>
       <c r="E49" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),325.7)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),339.75)</f>
         <v/>
       </c>
       <c r="F49" s="6">
@@ -2135,21 +2135,21 @@
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>iPhone 17e</t>
+          <t>iPhone 17 Pro</t>
         </is>
       </c>
       <c r="B50" s="4" t="n">
-        <v>46092</v>
+        <v>45919</v>
       </c>
       <c r="C50" s="5" t="n">
-        <v>599</v>
+        <v>1099</v>
       </c>
       <c r="D50" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B50), 2, 2)"),314.97)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B50), 2, 2)"),245.5)</f>
         <v/>
       </c>
       <c r="E50" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),325.7)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),339.75)</f>
         <v/>
       </c>
       <c r="F50" s="6">
@@ -2165,35 +2165,167 @@
         <v/>
       </c>
     </row>
-    <row r="51" ht="24" customHeight="1">
-      <c r="A51" s="8" t="inlineStr">
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>iPhone 17 Pro Max</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="n">
+        <v>45919</v>
+      </c>
+      <c r="C51" s="5" t="n">
+        <v>1199</v>
+      </c>
+      <c r="D51" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B51), 2, 2)"),245.5)</f>
+        <v/>
+      </c>
+      <c r="E51" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),339.75)</f>
+        <v/>
+      </c>
+      <c r="F51" s="6">
+        <f>C51/D51*E51</f>
+        <v/>
+      </c>
+      <c r="G51" s="5">
+        <f>F51-C51</f>
+        <v/>
+      </c>
+      <c r="H51" s="7">
+        <f>(F51/C51)-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>iPhone 17e</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="n">
+        <v>46092</v>
+      </c>
+      <c r="C52" s="5" t="n">
+        <v>599</v>
+      </c>
+      <c r="D52" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B52), 2, 2)"),260.81)</f>
+        <v/>
+      </c>
+      <c r="E52" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),339.75)</f>
+        <v/>
+      </c>
+      <c r="F52" s="6">
+        <f>C52/D52*E52</f>
+        <v/>
+      </c>
+      <c r="G52" s="5">
+        <f>F52-C52</f>
+        <v/>
+      </c>
+      <c r="H52" s="7">
+        <f>(F52/C52)-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>iPhone 18 Pro</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="n">
+        <v>46283</v>
+      </c>
+      <c r="C53" s="5" t="n">
+        <v>1199</v>
+      </c>
+      <c r="D53" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B53), 2, 2)"),336.13)</f>
+        <v/>
+      </c>
+      <c r="E53" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),339.75)</f>
+        <v/>
+      </c>
+      <c r="F53" s="6">
+        <f>C53/D53*E53</f>
+        <v/>
+      </c>
+      <c r="G53" s="5">
+        <f>F53-C53</f>
+        <v/>
+      </c>
+      <c r="H53" s="7">
+        <f>(F53/C53)-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>iPhone 18 Pro Max</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="n">
+        <v>46283</v>
+      </c>
+      <c r="C54" s="5" t="n">
+        <v>1299</v>
+      </c>
+      <c r="D54" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price"", B54), 2, 2)"),336.13)</f>
+        <v/>
+      </c>
+      <c r="E54" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(GOOGLEFINANCE(""AAPL"", ""price""))"),339.75)</f>
+        <v/>
+      </c>
+      <c r="F54" s="6">
+        <f>C54/D54*E54</f>
+        <v/>
+      </c>
+      <c r="G54" s="5">
+        <f>F54-C54</f>
+        <v/>
+      </c>
+      <c r="H54" s="7">
+        <f>(F54/C54)-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" ht="24" customHeight="1">
+      <c r="A55" s="8" t="inlineStr">
         <is>
           <t>Total / Portfolio Summary</t>
         </is>
       </c>
-      <c r="B51" s="9" t="inlineStr">
-        <is>
-          <t>Updated: 2026-09-02</t>
-        </is>
-      </c>
-      <c r="C51" s="10">
-        <f>SUM(C2:C50)</f>
-        <v/>
-      </c>
-      <c r="D51" s="11" t="inlineStr"/>
-      <c r="E51" s="12" t="n">
-        <v>325.7</v>
-      </c>
-      <c r="F51" s="10">
-        <f>SUM(F2:F50)</f>
-        <v/>
-      </c>
-      <c r="G51" s="10">
-        <f>SUM(G2:G50)</f>
-        <v/>
-      </c>
-      <c r="H51" s="13">
-        <f>(F51/C51)-1</f>
+      <c r="B55" s="9" t="inlineStr">
+        <is>
+          <t>Updated: 2026-09-23</t>
+        </is>
+      </c>
+      <c r="C55" s="10">
+        <f>SUM(C2:C54)</f>
+        <v/>
+      </c>
+      <c r="D55" s="11" t="inlineStr"/>
+      <c r="E55" s="12" t="n">
+        <v>339.75</v>
+      </c>
+      <c r="F55" s="10">
+        <f>SUM(F2:F54)</f>
+        <v/>
+      </c>
+      <c r="G55" s="10">
+        <f>SUM(G2:G54)</f>
+        <v/>
+      </c>
+      <c r="H55" s="13">
+        <f>(F55/C55)-1</f>
         <v/>
       </c>
     </row>
